--- a/SAL_JIG/SAL_JIG_ES0/측정자료/color_debug/mobis_color_table_2025_01_08_최종버전.xlsx
+++ b/SAL_JIG/SAL_JIG_ES0/측정자료/color_debug/mobis_color_table_2025_01_08_최종버전.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\SAL_JIG\SAL_JIG_ES0\측정자료\color_debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2A270B-F798-468E-857D-C99BC28304AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6892C309-DE64-492C-911A-005D300D5D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="전문가색상 54색" sheetId="1" r:id="rId1"/>
@@ -2095,7 +2095,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="302">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2909,6 +2909,9 @@
     <xf numFmtId="0" fontId="0" fillId="107" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="69" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2922,19 +2925,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="69" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="69" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="140" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="140" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2942,34 +2960,13 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="69" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="140" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="140" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="69" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="69" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3165,7 +3162,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -4329,7 +4326,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7552,7 +7549,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -8297,7 +8294,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -9039,7 +9036,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -15746,8 +15743,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="31196280" y="381000"/>
-          <a:ext cx="4732431" cy="6877652"/>
+          <a:off x="31382698" y="372836"/>
+          <a:ext cx="4761006" cy="6722530"/>
           <a:chOff x="19533870" y="394335"/>
           <a:chExt cx="4745766" cy="6950042"/>
         </a:xfrm>
@@ -16515,33 +16512,33 @@
     <row r="2" spans="2:26" ht="15.75" customHeight="1">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="281" t="s">
+      <c r="D2" s="282" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="120"/>
-      <c r="F2" s="281" t="s">
+      <c r="F2" s="282" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="281"/>
-      <c r="H2" s="281" t="s">
+      <c r="G2" s="282"/>
+      <c r="H2" s="282" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="281"/>
-      <c r="J2" s="281"/>
-      <c r="L2" s="281" t="s">
+      <c r="I2" s="282"/>
+      <c r="J2" s="282"/>
+      <c r="L2" s="282" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="281"/>
-      <c r="N2" s="281"/>
-      <c r="O2" s="281"/>
-      <c r="P2" s="281"/>
+      <c r="M2" s="282"/>
+      <c r="N2" s="282"/>
+      <c r="O2" s="282"/>
+      <c r="P2" s="282"/>
     </row>
     <row r="3" spans="2:26" ht="15.75" customHeight="1">
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="281"/>
+      <c r="D3" s="282"/>
       <c r="E3" s="120" t="s">
         <v>13</v>
       </c>
@@ -16605,7 +16602,7 @@
       </c>
     </row>
     <row r="4" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B4" s="282" t="s">
+      <c r="B4" s="283" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="70"/>
@@ -16677,7 +16674,7 @@
       </c>
     </row>
     <row r="5" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B5" s="282"/>
+      <c r="B5" s="283"/>
       <c r="C5" s="71"/>
       <c r="D5" s="121">
         <v>2</v>
@@ -16747,7 +16744,7 @@
       </c>
     </row>
     <row r="6" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B6" s="282"/>
+      <c r="B6" s="283"/>
       <c r="C6" s="72"/>
       <c r="D6" s="121">
         <v>3</v>
@@ -16817,7 +16814,7 @@
       </c>
     </row>
     <row r="7" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B7" s="282"/>
+      <c r="B7" s="283"/>
       <c r="C7" s="73"/>
       <c r="D7" s="121">
         <v>4</v>
@@ -16887,7 +16884,7 @@
       </c>
     </row>
     <row r="8" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B8" s="282"/>
+      <c r="B8" s="283"/>
       <c r="C8" s="74"/>
       <c r="D8" s="121">
         <v>5</v>
@@ -16957,7 +16954,7 @@
       </c>
     </row>
     <row r="9" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B9" s="282"/>
+      <c r="B9" s="283"/>
       <c r="C9" s="75"/>
       <c r="D9" s="121">
         <v>6</v>
@@ -17027,7 +17024,7 @@
       </c>
     </row>
     <row r="10" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B10" s="282"/>
+      <c r="B10" s="283"/>
       <c r="C10" s="76"/>
       <c r="D10" s="121">
         <v>7</v>
@@ -17097,7 +17094,7 @@
       </c>
     </row>
     <row r="11" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B11" s="282"/>
+      <c r="B11" s="283"/>
       <c r="C11" s="77"/>
       <c r="D11" s="121">
         <v>8</v>
@@ -17167,7 +17164,7 @@
       </c>
     </row>
     <row r="12" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B12" s="282"/>
+      <c r="B12" s="283"/>
       <c r="C12" s="78"/>
       <c r="D12" s="121">
         <v>9</v>
@@ -17238,7 +17235,7 @@
       </c>
     </row>
     <row r="13" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B13" s="282"/>
+      <c r="B13" s="283"/>
       <c r="C13" s="79"/>
       <c r="D13" s="121">
         <v>10</v>
@@ -17308,7 +17305,7 @@
       </c>
     </row>
     <row r="14" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B14" s="282" t="s">
+      <c r="B14" s="283" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="80"/>
@@ -17380,7 +17377,7 @@
       </c>
     </row>
     <row r="15" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B15" s="282"/>
+      <c r="B15" s="283"/>
       <c r="C15" s="81"/>
       <c r="D15" s="121">
         <v>12</v>
@@ -17450,7 +17447,7 @@
       </c>
     </row>
     <row r="16" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B16" s="282"/>
+      <c r="B16" s="283"/>
       <c r="C16" s="82"/>
       <c r="D16" s="121">
         <v>13</v>
@@ -17520,7 +17517,7 @@
       </c>
     </row>
     <row r="17" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B17" s="282"/>
+      <c r="B17" s="283"/>
       <c r="C17" s="83"/>
       <c r="D17" s="121">
         <v>14</v>
@@ -17590,7 +17587,7 @@
       </c>
     </row>
     <row r="18" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B18" s="282"/>
+      <c r="B18" s="283"/>
       <c r="C18" s="84"/>
       <c r="D18" s="121">
         <v>15</v>
@@ -17660,7 +17657,7 @@
       </c>
     </row>
     <row r="19" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B19" s="282"/>
+      <c r="B19" s="283"/>
       <c r="C19" s="85"/>
       <c r="D19" s="121">
         <v>16</v>
@@ -17730,7 +17727,7 @@
       </c>
     </row>
     <row r="20" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B20" s="282"/>
+      <c r="B20" s="283"/>
       <c r="C20" s="86"/>
       <c r="D20" s="121">
         <v>17</v>
@@ -17800,7 +17797,7 @@
       </c>
     </row>
     <row r="21" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B21" s="282"/>
+      <c r="B21" s="283"/>
       <c r="C21" s="87"/>
       <c r="D21" s="121">
         <v>18</v>
@@ -17870,7 +17867,7 @@
       </c>
     </row>
     <row r="22" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B22" s="282"/>
+      <c r="B22" s="283"/>
       <c r="C22" s="88"/>
       <c r="D22" s="121">
         <v>19</v>
@@ -17940,7 +17937,7 @@
       </c>
     </row>
     <row r="23" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B23" s="282"/>
+      <c r="B23" s="283"/>
       <c r="C23" s="89"/>
       <c r="D23" s="121">
         <v>20</v>
@@ -18010,7 +18007,7 @@
       </c>
     </row>
     <row r="24" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B24" s="282" t="s">
+      <c r="B24" s="283" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="90"/>
@@ -18082,7 +18079,7 @@
       </c>
     </row>
     <row r="25" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B25" s="282"/>
+      <c r="B25" s="283"/>
       <c r="C25" s="91"/>
       <c r="D25" s="121">
         <v>22</v>
@@ -18152,7 +18149,7 @@
       </c>
     </row>
     <row r="26" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B26" s="282"/>
+      <c r="B26" s="283"/>
       <c r="C26" s="92"/>
       <c r="D26" s="121">
         <v>23</v>
@@ -18222,7 +18219,7 @@
       </c>
     </row>
     <row r="27" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B27" s="282"/>
+      <c r="B27" s="283"/>
       <c r="C27" s="93"/>
       <c r="D27" s="121">
         <v>24</v>
@@ -18292,7 +18289,7 @@
       </c>
     </row>
     <row r="28" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B28" s="282"/>
+      <c r="B28" s="283"/>
       <c r="C28" s="94"/>
       <c r="D28" s="121">
         <v>25</v>
@@ -18362,7 +18359,7 @@
       </c>
     </row>
     <row r="29" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B29" s="282"/>
+      <c r="B29" s="283"/>
       <c r="C29" s="95"/>
       <c r="D29" s="121">
         <v>26</v>
@@ -18432,7 +18429,7 @@
       </c>
     </row>
     <row r="30" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B30" s="282"/>
+      <c r="B30" s="283"/>
       <c r="C30" s="96"/>
       <c r="D30" s="121">
         <v>27</v>
@@ -18502,7 +18499,7 @@
       </c>
     </row>
     <row r="31" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B31" s="282"/>
+      <c r="B31" s="283"/>
       <c r="C31" s="97"/>
       <c r="D31" s="121">
         <v>28</v>
@@ -18572,7 +18569,7 @@
       </c>
     </row>
     <row r="32" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B32" s="282"/>
+      <c r="B32" s="283"/>
       <c r="C32" s="98"/>
       <c r="D32" s="121">
         <v>29</v>
@@ -18642,7 +18639,7 @@
       </c>
     </row>
     <row r="33" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B33" s="282"/>
+      <c r="B33" s="283"/>
       <c r="C33" s="99"/>
       <c r="D33" s="121">
         <v>30</v>
@@ -18712,7 +18709,7 @@
       </c>
     </row>
     <row r="34" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B34" s="282" t="s">
+      <c r="B34" s="283" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="100"/>
@@ -18784,7 +18781,7 @@
       </c>
     </row>
     <row r="35" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B35" s="282"/>
+      <c r="B35" s="283"/>
       <c r="C35" s="101"/>
       <c r="D35" s="121">
         <v>32</v>
@@ -18855,7 +18852,7 @@
       </c>
     </row>
     <row r="36" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B36" s="282"/>
+      <c r="B36" s="283"/>
       <c r="C36" s="102"/>
       <c r="D36" s="121">
         <v>33</v>
@@ -18925,7 +18922,7 @@
       </c>
     </row>
     <row r="37" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B37" s="282"/>
+      <c r="B37" s="283"/>
       <c r="C37" s="101"/>
       <c r="D37" s="121">
         <v>34</v>
@@ -18994,7 +18991,7 @@
       <c r="Z37" s="144"/>
     </row>
     <row r="38" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B38" s="282"/>
+      <c r="B38" s="283"/>
       <c r="C38" s="103"/>
       <c r="D38" s="121">
         <v>35</v>
@@ -19064,7 +19061,7 @@
       </c>
     </row>
     <row r="39" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B39" s="282"/>
+      <c r="B39" s="283"/>
       <c r="C39" s="104"/>
       <c r="D39" s="121">
         <v>36</v>
@@ -19134,7 +19131,7 @@
       </c>
     </row>
     <row r="40" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B40" s="282"/>
+      <c r="B40" s="283"/>
       <c r="C40" s="105"/>
       <c r="D40" s="121">
         <v>37</v>
@@ -19204,7 +19201,7 @@
       </c>
     </row>
     <row r="41" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B41" s="282"/>
+      <c r="B41" s="283"/>
       <c r="C41" s="106"/>
       <c r="D41" s="121">
         <v>38</v>
@@ -19274,7 +19271,7 @@
       </c>
     </row>
     <row r="42" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B42" s="282"/>
+      <c r="B42" s="283"/>
       <c r="C42" s="107"/>
       <c r="D42" s="121">
         <v>39</v>
@@ -19344,7 +19341,7 @@
       </c>
     </row>
     <row r="43" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B43" s="282"/>
+      <c r="B43" s="283"/>
       <c r="C43" s="100"/>
       <c r="D43" s="121">
         <v>40</v>
@@ -19414,7 +19411,7 @@
       </c>
     </row>
     <row r="44" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B44" s="282"/>
+      <c r="B44" s="283"/>
       <c r="C44" s="108"/>
       <c r="D44" s="121">
         <v>41</v>
@@ -19484,7 +19481,7 @@
       </c>
     </row>
     <row r="45" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B45" s="282"/>
+      <c r="B45" s="283"/>
       <c r="C45" s="101"/>
       <c r="D45" s="121">
         <v>42</v>
@@ -19555,7 +19552,7 @@
       </c>
     </row>
     <row r="46" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B46" s="282" t="s">
+      <c r="B46" s="283" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="87"/>
@@ -19627,7 +19624,7 @@
       </c>
     </row>
     <row r="47" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B47" s="282"/>
+      <c r="B47" s="283"/>
       <c r="C47" s="109"/>
       <c r="D47" s="121">
         <v>44</v>
@@ -19697,7 +19694,7 @@
       </c>
     </row>
     <row r="48" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B48" s="282"/>
+      <c r="B48" s="283"/>
       <c r="C48" s="110"/>
       <c r="D48" s="121">
         <v>45</v>
@@ -19767,7 +19764,7 @@
       </c>
     </row>
     <row r="49" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B49" s="282"/>
+      <c r="B49" s="283"/>
       <c r="C49" s="110"/>
       <c r="D49" s="121">
         <v>46</v>
@@ -19837,7 +19834,7 @@
       </c>
     </row>
     <row r="50" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B50" s="282"/>
+      <c r="B50" s="283"/>
       <c r="C50" s="111"/>
       <c r="D50" s="121">
         <v>47</v>
@@ -19907,7 +19904,7 @@
       </c>
     </row>
     <row r="51" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B51" s="282"/>
+      <c r="B51" s="283"/>
       <c r="C51" s="112"/>
       <c r="D51" s="121">
         <v>48</v>
@@ -19977,7 +19974,7 @@
       </c>
     </row>
     <row r="52" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B52" s="282"/>
+      <c r="B52" s="283"/>
       <c r="C52" s="113"/>
       <c r="D52" s="121">
         <v>49</v>
@@ -20047,7 +20044,7 @@
       </c>
     </row>
     <row r="53" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B53" s="282"/>
+      <c r="B53" s="283"/>
       <c r="C53" s="114"/>
       <c r="D53" s="121">
         <v>50</v>
@@ -20119,7 +20116,7 @@
       </c>
     </row>
     <row r="54" spans="2:26" ht="15.75" customHeight="1">
-      <c r="B54" s="282"/>
+      <c r="B54" s="283"/>
       <c r="C54" s="112"/>
       <c r="D54" s="121">
         <v>51</v>
@@ -20230,43 +20227,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B2" s="283" t="s">
+      <c r="B2" s="284" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="284" t="s">
+      <c r="C2" s="285" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="281" t="s">
+      <c r="D2" s="282" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="281"/>
-      <c r="F2" s="281" t="s">
+      <c r="E2" s="282"/>
+      <c r="F2" s="282" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="281"/>
-      <c r="H2" s="281"/>
-      <c r="J2" s="281" t="s">
+      <c r="G2" s="282"/>
+      <c r="H2" s="282"/>
+      <c r="J2" s="282" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="281"/>
-      <c r="L2" s="281" t="s">
+      <c r="K2" s="282"/>
+      <c r="L2" s="282" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="281"/>
-      <c r="N2" s="281"/>
-      <c r="O2" s="281" t="s">
+      <c r="M2" s="282"/>
+      <c r="N2" s="282"/>
+      <c r="O2" s="282" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="281"/>
-      <c r="Q2" s="281" t="s">
+      <c r="P2" s="282"/>
+      <c r="Q2" s="282" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="281"/>
-      <c r="S2" s="281"/>
+      <c r="R2" s="282"/>
+      <c r="S2" s="282"/>
     </row>
     <row r="3" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B3" s="283"/>
-      <c r="C3" s="284"/>
+      <c r="B3" s="284"/>
+      <c r="C3" s="285"/>
       <c r="D3" s="120" t="s">
         <v>0</v>
       </c>
@@ -25044,83 +25041,83 @@
       <c r="B3" s="287" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="281" t="s">
+      <c r="C3" s="282" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="281"/>
-      <c r="F3" s="281" t="s">
+      <c r="E3" s="282"/>
+      <c r="F3" s="282" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="286"/>
-      <c r="H3" s="285" t="s">
+      <c r="G3" s="289"/>
+      <c r="H3" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="285"/>
-      <c r="J3" s="285"/>
+      <c r="I3" s="290"/>
+      <c r="J3" s="290"/>
       <c r="K3" s="287" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="281" t="s">
+      <c r="L3" s="282" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="281" t="s">
+      <c r="M3" s="282" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="281"/>
-      <c r="O3" s="281" t="s">
+      <c r="N3" s="282"/>
+      <c r="O3" s="282" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="286"/>
-      <c r="Q3" s="285" t="s">
+      <c r="P3" s="289"/>
+      <c r="Q3" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="285"/>
-      <c r="S3" s="285"/>
+      <c r="R3" s="290"/>
+      <c r="S3" s="290"/>
       <c r="T3" s="287" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="281" t="s">
+      <c r="U3" s="282" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="281" t="s">
+      <c r="V3" s="282" t="s">
         <v>5</v>
       </c>
-      <c r="W3" s="281"/>
-      <c r="X3" s="281" t="s">
+      <c r="W3" s="282"/>
+      <c r="X3" s="282" t="s">
         <v>36</v>
       </c>
-      <c r="Y3" s="286"/>
-      <c r="Z3" s="285" t="s">
+      <c r="Y3" s="289"/>
+      <c r="Z3" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="AA3" s="285"/>
-      <c r="AB3" s="285"/>
+      <c r="AA3" s="290"/>
+      <c r="AB3" s="290"/>
       <c r="AC3" s="287" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="281" t="s">
+      <c r="AD3" s="282" t="s">
         <v>6</v>
       </c>
-      <c r="AE3" s="281" t="s">
+      <c r="AE3" s="282" t="s">
         <v>5</v>
       </c>
-      <c r="AF3" s="281"/>
-      <c r="AG3" s="281" t="s">
+      <c r="AF3" s="282"/>
+      <c r="AG3" s="282" t="s">
         <v>36</v>
       </c>
-      <c r="AH3" s="286"/>
-      <c r="AI3" s="285" t="s">
+      <c r="AH3" s="289"/>
+      <c r="AI3" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="AJ3" s="285"/>
-      <c r="AK3" s="285"/>
+      <c r="AJ3" s="290"/>
+      <c r="AK3" s="290"/>
     </row>
     <row r="4" spans="2:37">
       <c r="B4" s="288"/>
-      <c r="C4" s="281"/>
+      <c r="C4" s="282"/>
       <c r="D4" s="161" t="s">
         <v>0</v>
       </c>
@@ -25143,7 +25140,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="288"/>
-      <c r="L4" s="281"/>
+      <c r="L4" s="282"/>
       <c r="M4" s="161" t="s">
         <v>0</v>
       </c>
@@ -25166,7 +25163,7 @@
         <v>33</v>
       </c>
       <c r="T4" s="288"/>
-      <c r="U4" s="281"/>
+      <c r="U4" s="282"/>
       <c r="V4" s="161" t="s">
         <v>0</v>
       </c>
@@ -25189,7 +25186,7 @@
         <v>33</v>
       </c>
       <c r="AC4" s="288"/>
-      <c r="AD4" s="281"/>
+      <c r="AD4" s="282"/>
       <c r="AE4" s="161" t="s">
         <v>0</v>
       </c>
@@ -27039,12 +27036,12 @@
     <row r="21" spans="2:37">
       <c r="AC21" s="232"/>
       <c r="AD21" s="232"/>
-      <c r="AE21" s="289" t="s">
+      <c r="AE21" s="286" t="s">
         <v>35</v>
       </c>
-      <c r="AF21" s="289"/>
-      <c r="AG21" s="289"/>
-      <c r="AH21" s="289"/>
+      <c r="AF21" s="286"/>
+      <c r="AG21" s="286"/>
+      <c r="AH21" s="286"/>
       <c r="AI21" s="228">
         <f>AVERAGE(H5:H20,Q5:Q20,Z5:Z20,AI5:AI20)</f>
         <v>1.2656250000000029E-3</v>
@@ -27060,6 +27057,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AB3"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
     <mergeCell ref="AE21:AH21"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="K3:K4"/>
@@ -27074,13 +27078,6 @@
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AB3"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27110,84 +27107,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:46">
-      <c r="B2" s="295"/>
+      <c r="B2" s="293"/>
       <c r="C2" s="234"/>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="291" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="292"/>
-      <c r="F2" s="293" t="s">
+      <c r="E2" s="291"/>
+      <c r="F2" s="292" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="293"/>
-      <c r="H2" s="293" t="s">
+      <c r="G2" s="292"/>
+      <c r="H2" s="292" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="293"/>
-      <c r="J2" s="293"/>
-      <c r="K2" s="291"/>
+      <c r="I2" s="292"/>
+      <c r="J2" s="292"/>
+      <c r="K2" s="297"/>
       <c r="L2" s="234"/>
-      <c r="M2" s="292" t="s">
+      <c r="M2" s="291" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="292"/>
-      <c r="O2" s="293" t="s">
+      <c r="N2" s="291"/>
+      <c r="O2" s="292" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="293"/>
-      <c r="Q2" s="293" t="s">
+      <c r="P2" s="292"/>
+      <c r="Q2" s="292" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="293"/>
-      <c r="S2" s="293"/>
-      <c r="T2" s="291"/>
+      <c r="R2" s="292"/>
+      <c r="S2" s="292"/>
+      <c r="T2" s="297"/>
       <c r="U2" s="234"/>
-      <c r="V2" s="292" t="s">
+      <c r="V2" s="291" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="292"/>
-      <c r="X2" s="293" t="s">
+      <c r="W2" s="291"/>
+      <c r="X2" s="292" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="293"/>
-      <c r="Z2" s="293" t="s">
+      <c r="Y2" s="292"/>
+      <c r="Z2" s="292" t="s">
         <v>39</v>
       </c>
-      <c r="AA2" s="293"/>
-      <c r="AB2" s="293"/>
-      <c r="AC2" s="291"/>
+      <c r="AA2" s="292"/>
+      <c r="AB2" s="292"/>
+      <c r="AC2" s="297"/>
       <c r="AD2" s="234"/>
-      <c r="AE2" s="292" t="s">
+      <c r="AE2" s="291" t="s">
         <v>5</v>
       </c>
-      <c r="AF2" s="292"/>
-      <c r="AG2" s="293" t="s">
+      <c r="AF2" s="291"/>
+      <c r="AG2" s="292" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="293"/>
-      <c r="AI2" s="293" t="s">
+      <c r="AH2" s="292"/>
+      <c r="AI2" s="292" t="s">
         <v>39</v>
       </c>
-      <c r="AJ2" s="293"/>
-      <c r="AK2" s="293"/>
-      <c r="AL2" s="291"/>
+      <c r="AJ2" s="292"/>
+      <c r="AK2" s="292"/>
+      <c r="AL2" s="297"/>
       <c r="AM2" s="234"/>
-      <c r="AN2" s="292" t="s">
+      <c r="AN2" s="291" t="s">
         <v>5</v>
       </c>
-      <c r="AO2" s="292"/>
-      <c r="AP2" s="293" t="s">
+      <c r="AO2" s="291"/>
+      <c r="AP2" s="292" t="s">
         <v>38</v>
       </c>
-      <c r="AQ2" s="293"/>
-      <c r="AR2" s="293" t="s">
+      <c r="AQ2" s="292"/>
+      <c r="AR2" s="292" t="s">
         <v>39</v>
       </c>
-      <c r="AS2" s="293"/>
-      <c r="AT2" s="293"/>
+      <c r="AS2" s="292"/>
+      <c r="AT2" s="292"/>
     </row>
     <row r="3" spans="2:46">
-      <c r="B3" s="295"/>
+      <c r="B3" s="293"/>
       <c r="C3" s="234" t="s">
         <v>6</v>
       </c>
@@ -27212,7 +27209,7 @@
       <c r="J3" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="291"/>
+      <c r="K3" s="297"/>
       <c r="L3" s="234" t="s">
         <v>6</v>
       </c>
@@ -27237,7 +27234,7 @@
       <c r="S3" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="291"/>
+      <c r="T3" s="297"/>
       <c r="U3" s="234" t="s">
         <v>6</v>
       </c>
@@ -27262,7 +27259,7 @@
       <c r="AB3" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="AC3" s="291"/>
+      <c r="AC3" s="297"/>
       <c r="AD3" s="234" t="s">
         <v>6</v>
       </c>
@@ -27287,7 +27284,7 @@
       <c r="AK3" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="AL3" s="291"/>
+      <c r="AL3" s="297"/>
       <c r="AM3" s="234" t="s">
         <v>6</v>
       </c>
@@ -27314,7 +27311,7 @@
       </c>
     </row>
     <row r="4" spans="2:46">
-      <c r="B4" s="296" t="s">
+      <c r="B4" s="294" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="70"/>
@@ -27342,7 +27339,7 @@
         <f>SQRT(H4^2+I4^2)</f>
         <v>1.4257980221616352E-3</v>
       </c>
-      <c r="K4" s="294" t="s">
+      <c r="K4" s="295" t="s">
         <v>8</v>
       </c>
       <c r="L4" s="242"/>
@@ -27370,7 +27367,7 @@
         <f t="shared" ref="S4:S13" si="2">SQRT(Q4^2+R4^2)</f>
         <v>6.0605280298008254E-4</v>
       </c>
-      <c r="T4" s="294" t="s">
+      <c r="T4" s="295" t="s">
         <v>9</v>
       </c>
       <c r="U4" s="244"/>
@@ -27398,7 +27395,7 @@
         <f t="shared" ref="AB4:AB13" si="5">SQRT(Z4^2+AA4^2)</f>
         <v>2.2105429197371738E-3</v>
       </c>
-      <c r="AC4" s="294" t="s">
+      <c r="AC4" s="295" t="s">
         <v>10</v>
       </c>
       <c r="AD4" s="245"/>
@@ -27426,7 +27423,7 @@
         <f t="shared" ref="AK4:AK15" si="8">SQRT(AI4^2+AJ4^2)</f>
         <v>1.5498387012847633E-3</v>
       </c>
-      <c r="AL4" s="294" t="s">
+      <c r="AL4" s="295" t="s">
         <v>37</v>
       </c>
       <c r="AM4" s="246"/>
@@ -27456,7 +27453,7 @@
       </c>
     </row>
     <row r="5" spans="2:46">
-      <c r="B5" s="296"/>
+      <c r="B5" s="294"/>
       <c r="C5" s="71"/>
       <c r="D5" s="243">
         <v>0.32937</v>
@@ -27482,7 +27479,7 @@
         <f t="shared" ref="J5:J13" si="14">SQRT(H5^2+I5^2)</f>
         <v>1.5250573759698213E-3</v>
       </c>
-      <c r="K5" s="294"/>
+      <c r="K5" s="295"/>
       <c r="L5" s="247"/>
       <c r="M5" s="243">
         <v>0.30370999999999998</v>
@@ -27508,7 +27505,7 @@
         <f t="shared" si="2"/>
         <v>1.4900335566691346E-3</v>
       </c>
-      <c r="T5" s="294"/>
+      <c r="T5" s="295"/>
       <c r="U5" s="248"/>
       <c r="V5" s="243">
         <v>0.51129999999999998</v>
@@ -27534,7 +27531,7 @@
         <f t="shared" si="5"/>
         <v>4.3863424398919406E-4</v>
       </c>
-      <c r="AC5" s="294"/>
+      <c r="AC5" s="295"/>
       <c r="AD5" s="249"/>
       <c r="AE5" s="243">
         <v>0.21</v>
@@ -27560,7 +27557,7 @@
         <f t="shared" si="8"/>
         <v>3.0016662039607185E-2</v>
       </c>
-      <c r="AL5" s="294"/>
+      <c r="AL5" s="295"/>
       <c r="AM5" s="109"/>
       <c r="AN5" s="243">
         <v>0.18448000000000001</v>
@@ -27588,7 +27585,7 @@
       </c>
     </row>
     <row r="6" spans="2:46">
-      <c r="B6" s="296"/>
+      <c r="B6" s="294"/>
       <c r="C6" s="72"/>
       <c r="D6" s="243">
         <v>0.51727999999999996</v>
@@ -27614,7 +27611,7 @@
         <f t="shared" si="14"/>
         <v>8.1412529748194854E-4</v>
       </c>
-      <c r="K6" s="294"/>
+      <c r="K6" s="295"/>
       <c r="L6" s="250"/>
       <c r="M6" s="243">
         <v>0.26643</v>
@@ -27640,7 +27637,7 @@
         <f t="shared" si="2"/>
         <v>5.7218878003681309E-4</v>
       </c>
-      <c r="T6" s="294"/>
+      <c r="T6" s="295"/>
       <c r="U6" s="251"/>
       <c r="V6" s="243">
         <v>0.60202999999999995</v>
@@ -27666,7 +27663,7 @@
         <f t="shared" si="5"/>
         <v>1.115078472574933E-3</v>
       </c>
-      <c r="AC6" s="294"/>
+      <c r="AC6" s="295"/>
       <c r="AD6" s="252"/>
       <c r="AE6" s="243">
         <v>0.47871000000000002</v>
@@ -27692,7 +27689,7 @@
         <f t="shared" si="8"/>
         <v>2.2484883811129735E-3</v>
       </c>
-      <c r="AL6" s="294"/>
+      <c r="AL6" s="295"/>
       <c r="AM6" s="110"/>
       <c r="AN6" s="243">
         <v>0.60940000000000005</v>
@@ -27720,7 +27717,7 @@
       </c>
     </row>
     <row r="7" spans="2:46">
-      <c r="B7" s="296"/>
+      <c r="B7" s="294"/>
       <c r="C7" s="73"/>
       <c r="D7" s="243">
         <v>0.58682999999999996</v>
@@ -27746,7 +27743,7 @@
         <f t="shared" si="14"/>
         <v>2.180481598179641E-3</v>
       </c>
-      <c r="K7" s="294"/>
+      <c r="K7" s="295"/>
       <c r="L7" s="253"/>
       <c r="M7" s="243">
         <v>0.39599000000000001</v>
@@ -27772,7 +27769,7 @@
         <f t="shared" si="2"/>
         <v>2.1023796041633029E-4</v>
       </c>
-      <c r="T7" s="294"/>
+      <c r="T7" s="295"/>
       <c r="U7" s="254"/>
       <c r="V7" s="243">
         <v>0.62704000000000004</v>
@@ -27798,7 +27795,7 @@
         <f t="shared" si="5"/>
         <v>2.140373799129442E-3</v>
       </c>
-      <c r="AC7" s="294"/>
+      <c r="AC7" s="295"/>
       <c r="AD7" s="249"/>
       <c r="AE7" s="243">
         <v>0.21</v>
@@ -27824,7 +27821,7 @@
         <f t="shared" si="8"/>
         <v>3.0016662039607185E-2</v>
       </c>
-      <c r="AL7" s="294"/>
+      <c r="AL7" s="295"/>
       <c r="AM7" s="110"/>
       <c r="AN7" s="243">
         <v>0.60940000000000005</v>
@@ -27852,7 +27849,7 @@
       </c>
     </row>
     <row r="8" spans="2:46">
-      <c r="B8" s="296"/>
+      <c r="B8" s="294"/>
       <c r="C8" s="74"/>
       <c r="D8" s="255">
         <v>0.29699999999999999</v>
@@ -27878,7 +27875,7 @@
         <f t="shared" si="14"/>
         <v>2.236067977499792E-3</v>
       </c>
-      <c r="K8" s="294"/>
+      <c r="K8" s="295"/>
       <c r="L8" s="256"/>
       <c r="M8" s="243">
         <v>0.49687999999999999</v>
@@ -27904,7 +27901,7 @@
         <f t="shared" si="2"/>
         <v>1.7773013250431118E-3</v>
       </c>
-      <c r="T8" s="294"/>
+      <c r="T8" s="295"/>
       <c r="U8" s="257"/>
       <c r="V8" s="243">
         <v>0.63944999999999996</v>
@@ -27930,7 +27927,7 @@
         <f t="shared" si="5"/>
         <v>2.022992832414445E-3</v>
       </c>
-      <c r="AC8" s="294"/>
+      <c r="AC8" s="295"/>
       <c r="AD8" s="258"/>
       <c r="AE8" s="243">
         <v>0.64</v>
@@ -27956,7 +27953,7 @@
         <f t="shared" si="8"/>
         <v>2.236067977499792E-3</v>
       </c>
-      <c r="AL8" s="294"/>
+      <c r="AL8" s="295"/>
       <c r="AM8" s="111"/>
       <c r="AN8" s="243">
         <v>0.16633999999999999</v>
@@ -27984,7 +27981,7 @@
       </c>
     </row>
     <row r="9" spans="2:46">
-      <c r="B9" s="296"/>
+      <c r="B9" s="294"/>
       <c r="C9" s="75"/>
       <c r="D9" s="243">
         <v>0.22844</v>
@@ -28010,7 +28007,7 @@
         <f t="shared" si="14"/>
         <v>6.9656299069071649E-4</v>
       </c>
-      <c r="K9" s="294"/>
+      <c r="K9" s="295"/>
       <c r="L9" s="259"/>
       <c r="M9" s="243">
         <v>0.43759999999999999</v>
@@ -28036,7 +28033,7 @@
         <f t="shared" si="2"/>
         <v>9.84885780179626E-4</v>
       </c>
-      <c r="T9" s="294"/>
+      <c r="T9" s="295"/>
       <c r="U9" s="260"/>
       <c r="V9" s="243">
         <v>0.26593</v>
@@ -28062,7 +28059,7 @@
         <f t="shared" si="5"/>
         <v>9.377099764852529E-4</v>
       </c>
-      <c r="AC9" s="294"/>
+      <c r="AC9" s="295"/>
       <c r="AD9" s="261"/>
       <c r="AE9" s="243">
         <v>0.60116999999999998</v>
@@ -28088,7 +28085,7 @@
         <f t="shared" si="8"/>
         <v>2.5894014752448429E-3</v>
       </c>
-      <c r="AL9" s="294"/>
+      <c r="AL9" s="295"/>
       <c r="AM9" s="112"/>
       <c r="AN9" s="243">
         <v>0.22803000000000001</v>
@@ -28116,7 +28113,7 @@
       </c>
     </row>
     <row r="10" spans="2:46">
-      <c r="B10" s="296"/>
+      <c r="B10" s="294"/>
       <c r="C10" s="76"/>
       <c r="D10" s="243">
         <v>0.16152</v>
@@ -28142,7 +28139,7 @@
         <f t="shared" si="14"/>
         <v>5.3851648071344372E-4</v>
       </c>
-      <c r="K10" s="294"/>
+      <c r="K10" s="295"/>
       <c r="L10" s="262"/>
       <c r="M10" s="243">
         <v>0.18945000000000001</v>
@@ -28168,7 +28165,7 @@
         <f t="shared" si="2"/>
         <v>1.2387897319561516E-3</v>
       </c>
-      <c r="T10" s="294"/>
+      <c r="T10" s="295"/>
       <c r="U10" s="263"/>
       <c r="V10" s="243">
         <v>0.19114999999999999</v>
@@ -28194,7 +28191,7 @@
         <f t="shared" si="5"/>
         <v>1.5784169284444654E-3</v>
       </c>
-      <c r="AC10" s="294"/>
+      <c r="AC10" s="295"/>
       <c r="AD10" s="264"/>
       <c r="AE10" s="243">
         <v>0.57308999999999999</v>
@@ -28220,7 +28217,7 @@
         <f t="shared" si="8"/>
         <v>1.3520724832641277E-3</v>
       </c>
-      <c r="AL10" s="294"/>
+      <c r="AL10" s="295"/>
       <c r="AM10" s="113"/>
       <c r="AN10" s="243">
         <v>0.25833</v>
@@ -28248,7 +28245,7 @@
       </c>
     </row>
     <row r="11" spans="2:46">
-      <c r="B11" s="296"/>
+      <c r="B11" s="294"/>
       <c r="C11" s="77"/>
       <c r="D11" s="243">
         <v>0.17596999999999999</v>
@@ -28274,7 +28271,7 @@
         <f t="shared" si="14"/>
         <v>1.1004090148667349E-3</v>
       </c>
-      <c r="K11" s="294"/>
+      <c r="K11" s="295"/>
       <c r="L11" s="246"/>
       <c r="M11" s="243">
         <v>0.31273000000000001</v>
@@ -28300,7 +28297,7 @@
         <f t="shared" si="2"/>
         <v>7.3027392121039814E-4</v>
       </c>
-      <c r="T11" s="294"/>
+      <c r="T11" s="295"/>
       <c r="U11" s="265"/>
       <c r="V11" s="243">
         <v>0.17471</v>
@@ -28326,7 +28323,7 @@
         <f t="shared" si="5"/>
         <v>7.1000000000001617E-4</v>
       </c>
-      <c r="AC11" s="294"/>
+      <c r="AC11" s="295"/>
       <c r="AD11" s="266"/>
       <c r="AE11" s="243">
         <v>0.20277999999999999</v>
@@ -28352,7 +28349,7 @@
         <f t="shared" si="8"/>
         <v>2.221440973782561E-3</v>
       </c>
-      <c r="AL11" s="294"/>
+      <c r="AL11" s="295"/>
       <c r="AM11" s="114"/>
       <c r="AN11" s="243">
         <v>0.35955999999999999</v>
@@ -28380,7 +28377,7 @@
       </c>
     </row>
     <row r="12" spans="2:46">
-      <c r="B12" s="296"/>
+      <c r="B12" s="294"/>
       <c r="C12" s="78"/>
       <c r="D12" s="243">
         <v>0.31192999999999999</v>
@@ -28406,7 +28403,7 @@
         <f t="shared" si="14"/>
         <v>1.5280867121992753E-2</v>
       </c>
-      <c r="K12" s="294"/>
+      <c r="K12" s="295"/>
       <c r="L12" s="267"/>
       <c r="M12" s="243">
         <v>0.63990999999999998</v>
@@ -28432,7 +28429,7 @@
         <f t="shared" si="2"/>
         <v>1.0911461863563822E-3</v>
       </c>
-      <c r="T12" s="294"/>
+      <c r="T12" s="295"/>
       <c r="U12" s="268"/>
       <c r="V12" s="243">
         <v>0.18432000000000001</v>
@@ -28458,7 +28455,7 @@
         <f t="shared" si="5"/>
         <v>1.0575916035975485E-3</v>
       </c>
-      <c r="AC12" s="294"/>
+      <c r="AC12" s="295"/>
       <c r="AD12" s="269"/>
       <c r="AE12" s="243">
         <v>0.15068999999999999</v>
@@ -28484,7 +28481,7 @@
         <f t="shared" si="8"/>
         <v>1.4493101807411721E-3</v>
       </c>
-      <c r="AL12" s="294"/>
+      <c r="AL12" s="295"/>
       <c r="AM12" s="112"/>
       <c r="AN12" s="243">
         <v>0.22803000000000001</v>
@@ -28512,7 +28509,7 @@
       </c>
     </row>
     <row r="13" spans="2:46">
-      <c r="B13" s="296"/>
+      <c r="B13" s="294"/>
       <c r="C13" s="79"/>
       <c r="D13" s="243">
         <v>0.25833</v>
@@ -28538,7 +28535,7 @@
         <f t="shared" si="14"/>
         <v>7.1168813394633323E-4</v>
       </c>
-      <c r="K13" s="294"/>
+      <c r="K13" s="295"/>
       <c r="L13" s="270"/>
       <c r="M13" s="243">
         <v>0.27287</v>
@@ -28564,7 +28561,7 @@
         <f t="shared" si="2"/>
         <v>2.2327785380552036E-3</v>
       </c>
-      <c r="T13" s="294"/>
+      <c r="T13" s="295"/>
       <c r="U13" s="271"/>
       <c r="V13" s="243">
         <v>0.32716000000000001</v>
@@ -28590,7 +28587,7 @@
         <f t="shared" si="5"/>
         <v>1.9416487838943861E-4</v>
       </c>
-      <c r="AC13" s="294"/>
+      <c r="AC13" s="295"/>
       <c r="AD13" s="245"/>
       <c r="AE13" s="243">
         <v>0.15346000000000001</v>
@@ -28653,7 +28650,7 @@
       <c r="Z14" s="239"/>
       <c r="AA14" s="239"/>
       <c r="AB14" s="239"/>
-      <c r="AC14" s="294"/>
+      <c r="AC14" s="295"/>
       <c r="AD14" s="273"/>
       <c r="AE14" s="243">
         <v>0.19545000000000001</v>
@@ -28681,12 +28678,12 @@
       </c>
       <c r="AL14" s="239"/>
       <c r="AM14" s="239"/>
-      <c r="AN14" s="290" t="s">
+      <c r="AN14" s="296" t="s">
         <v>35</v>
       </c>
-      <c r="AO14" s="290"/>
-      <c r="AP14" s="290"/>
-      <c r="AQ14" s="290"/>
+      <c r="AO14" s="296"/>
+      <c r="AP14" s="296"/>
+      <c r="AQ14" s="296"/>
       <c r="AR14" s="233">
         <f>AVERAGE(H4:H13,Q4:Q13,Z4:Z13,AI4:AI15,AR4:AR12)</f>
         <v>2.1470588235293986E-4</v>
@@ -28727,7 +28724,7 @@
       <c r="Z15" s="239"/>
       <c r="AA15" s="239"/>
       <c r="AB15" s="239"/>
-      <c r="AC15" s="294"/>
+      <c r="AC15" s="295"/>
       <c r="AD15" s="249"/>
       <c r="AE15" s="243">
         <v>0.21</v>
@@ -28765,11 +28762,11 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B13"/>
-    <mergeCell ref="K4:K13"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AN2:AO2"/>
+    <mergeCell ref="AP2:AQ2"/>
     <mergeCell ref="AR2:AT2"/>
     <mergeCell ref="T4:T13"/>
     <mergeCell ref="AC4:AC15"/>
@@ -28786,11 +28783,11 @@
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AN2:AO2"/>
-    <mergeCell ref="AP2:AQ2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B13"/>
+    <mergeCell ref="K4:K13"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28827,28 +28824,28 @@
         <v>14</v>
       </c>
       <c r="E3" s="135"/>
-      <c r="F3" s="286" t="s">
+      <c r="F3" s="289" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="297"/>
-      <c r="H3" s="298"/>
-      <c r="I3" s="300"/>
-      <c r="J3" s="299" t="s">
+      <c r="G3" s="299"/>
+      <c r="H3" s="300"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="284" t="s">
+      <c r="K3" s="285" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="281" t="s">
+      <c r="L3" s="282" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="281"/>
-      <c r="N3" s="281" t="s">
+      <c r="M3" s="282"/>
+      <c r="N3" s="282" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="281"/>
-      <c r="P3" s="281"/>
-      <c r="Q3" s="300"/>
+      <c r="O3" s="282"/>
+      <c r="P3" s="282"/>
+      <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="2:20">
       <c r="B4" s="2"/>
@@ -28870,11 +28867,11 @@
       <c r="H4" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="301" t="s">
+      <c r="I4" s="281" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="299"/>
-      <c r="K4" s="284"/>
+      <c r="J4" s="298"/>
+      <c r="K4" s="285"/>
       <c r="L4" s="120" t="s">
         <v>0</v>
       </c>
@@ -28890,12 +28887,12 @@
       <c r="P4" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="301" t="s">
+      <c r="Q4" s="281" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:20">
-      <c r="B5" s="282" t="s">
+      <c r="B5" s="283" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="70"/>
@@ -28946,7 +28943,7 @@
       <c r="T5" s="137"/>
     </row>
     <row r="6" spans="2:20">
-      <c r="B6" s="282"/>
+      <c r="B6" s="283"/>
       <c r="C6" s="71"/>
       <c r="D6" s="1">
         <v>0.32800000000000001</v>
@@ -28964,7 +28961,7 @@
         <v>200</v>
       </c>
       <c r="I6" s="140" t="str">
-        <f t="shared" ref="I6:I68" si="0">_xlfn.CONCAT("{", F6, ",", G6, ",", H6, "}", ",")</f>
+        <f t="shared" ref="I6:I55" si="0">_xlfn.CONCAT("{", F6, ",", G6, ",", H6, "}", ",")</f>
         <v>{245,224,200},</v>
       </c>
       <c r="J6" s="1">
@@ -28992,7 +28989,7 @@
       </c>
     </row>
     <row r="7" spans="2:20">
-      <c r="B7" s="282"/>
+      <c r="B7" s="283"/>
       <c r="C7" s="72"/>
       <c r="D7" s="1">
         <v>0.51800000000000002</v>
@@ -29038,7 +29035,7 @@
       </c>
     </row>
     <row r="8" spans="2:20">
-      <c r="B8" s="282"/>
+      <c r="B8" s="283"/>
       <c r="C8" s="73"/>
       <c r="D8" s="1">
         <v>0.58799999999999997</v>
@@ -29084,7 +29081,7 @@
       </c>
     </row>
     <row r="9" spans="2:20">
-      <c r="B9" s="282"/>
+      <c r="B9" s="283"/>
       <c r="C9" s="74"/>
       <c r="D9" s="1">
         <v>0.29799999999999999</v>
@@ -29130,7 +29127,7 @@
       </c>
     </row>
     <row r="10" spans="2:20">
-      <c r="B10" s="282"/>
+      <c r="B10" s="283"/>
       <c r="C10" s="75"/>
       <c r="D10" s="1">
         <v>0.22800000000000001</v>
@@ -29176,7 +29173,7 @@
       </c>
     </row>
     <row r="11" spans="2:20">
-      <c r="B11" s="282"/>
+      <c r="B11" s="283"/>
       <c r="C11" s="76"/>
       <c r="D11" s="1">
         <v>0.161</v>
@@ -29222,7 +29219,7 @@
       </c>
     </row>
     <row r="12" spans="2:20">
-      <c r="B12" s="282"/>
+      <c r="B12" s="283"/>
       <c r="C12" s="77"/>
       <c r="D12" s="1">
         <v>0.17599999999999999</v>
@@ -29268,7 +29265,7 @@
       </c>
     </row>
     <row r="13" spans="2:20">
-      <c r="B13" s="282"/>
+      <c r="B13" s="283"/>
       <c r="C13" s="78"/>
       <c r="D13" s="145">
         <v>0.30299999999999999</v>
@@ -29314,7 +29311,7 @@
       </c>
     </row>
     <row r="14" spans="2:20">
-      <c r="B14" s="282"/>
+      <c r="B14" s="283"/>
       <c r="C14" s="79"/>
       <c r="D14" s="1">
         <v>0.25900000000000001</v>
@@ -29360,7 +29357,7 @@
       </c>
     </row>
     <row r="15" spans="2:20">
-      <c r="B15" s="282" t="s">
+      <c r="B15" s="283" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="80"/>
@@ -29408,7 +29405,7 @@
       </c>
     </row>
     <row r="16" spans="2:20">
-      <c r="B16" s="282"/>
+      <c r="B16" s="283"/>
       <c r="C16" s="81"/>
       <c r="D16" s="1">
         <v>0.30299999999999999</v>
@@ -29454,7 +29451,7 @@
       </c>
     </row>
     <row r="17" spans="2:17">
-      <c r="B17" s="282"/>
+      <c r="B17" s="283"/>
       <c r="C17" s="82"/>
       <c r="D17" s="1">
         <v>0.26700000000000002</v>
@@ -29500,7 +29497,7 @@
       </c>
     </row>
     <row r="18" spans="2:17">
-      <c r="B18" s="282"/>
+      <c r="B18" s="283"/>
       <c r="C18" s="83"/>
       <c r="D18" s="1">
         <v>0.39600000000000002</v>
@@ -29546,7 +29543,7 @@
       </c>
     </row>
     <row r="19" spans="2:17">
-      <c r="B19" s="282"/>
+      <c r="B19" s="283"/>
       <c r="C19" s="84"/>
       <c r="D19" s="1">
         <v>0.498</v>
@@ -29592,7 +29589,7 @@
       </c>
     </row>
     <row r="20" spans="2:17">
-      <c r="B20" s="282"/>
+      <c r="B20" s="283"/>
       <c r="C20" s="85"/>
       <c r="D20" s="1">
         <v>0.438</v>
@@ -29638,7 +29635,7 @@
       </c>
     </row>
     <row r="21" spans="2:17">
-      <c r="B21" s="282"/>
+      <c r="B21" s="283"/>
       <c r="C21" s="86"/>
       <c r="D21" s="1">
         <v>0.19</v>
@@ -29684,7 +29681,7 @@
       </c>
     </row>
     <row r="22" spans="2:17">
-      <c r="B22" s="282"/>
+      <c r="B22" s="283"/>
       <c r="C22" s="87"/>
       <c r="D22" s="1">
         <v>0.312</v>
@@ -29730,7 +29727,7 @@
       </c>
     </row>
     <row r="23" spans="2:17">
-      <c r="B23" s="282"/>
+      <c r="B23" s="283"/>
       <c r="C23" s="88"/>
       <c r="D23" s="1">
         <v>0.64100000000000001</v>
@@ -29776,7 +29773,7 @@
       </c>
     </row>
     <row r="24" spans="2:17">
-      <c r="B24" s="282"/>
+      <c r="B24" s="283"/>
       <c r="C24" s="89"/>
       <c r="D24" s="1">
         <v>0.27100000000000002</v>
@@ -29822,7 +29819,7 @@
       </c>
     </row>
     <row r="25" spans="2:17">
-      <c r="B25" s="282" t="s">
+      <c r="B25" s="283" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="90"/>
@@ -29870,7 +29867,7 @@
       </c>
     </row>
     <row r="26" spans="2:17">
-      <c r="B26" s="282"/>
+      <c r="B26" s="283"/>
       <c r="C26" s="91"/>
       <c r="D26" s="1">
         <v>0.51100000000000001</v>
@@ -29916,7 +29913,7 @@
       </c>
     </row>
     <row r="27" spans="2:17">
-      <c r="B27" s="282"/>
+      <c r="B27" s="283"/>
       <c r="C27" s="92"/>
       <c r="D27" s="1">
         <v>0.60299999999999998</v>
@@ -29962,7 +29959,7 @@
       </c>
     </row>
     <row r="28" spans="2:17">
-      <c r="B28" s="282"/>
+      <c r="B28" s="283"/>
       <c r="C28" s="93"/>
       <c r="D28" s="1">
         <v>0.629</v>
@@ -30008,7 +30005,7 @@
       </c>
     </row>
     <row r="29" spans="2:17">
-      <c r="B29" s="282"/>
+      <c r="B29" s="283"/>
       <c r="C29" s="94"/>
       <c r="D29" s="1">
         <v>0.64100000000000001</v>
@@ -30054,7 +30051,7 @@
       </c>
     </row>
     <row r="30" spans="2:17">
-      <c r="B30" s="282"/>
+      <c r="B30" s="283"/>
       <c r="C30" s="95"/>
       <c r="D30" s="1">
         <v>0.26500000000000001</v>
@@ -30100,7 +30097,7 @@
       </c>
     </row>
     <row r="31" spans="2:17">
-      <c r="B31" s="282"/>
+      <c r="B31" s="283"/>
       <c r="C31" s="96"/>
       <c r="D31" s="1">
         <v>0.192</v>
@@ -30146,7 +30143,7 @@
       </c>
     </row>
     <row r="32" spans="2:17">
-      <c r="B32" s="282"/>
+      <c r="B32" s="283"/>
       <c r="C32" s="97"/>
       <c r="D32" s="1">
         <v>0.17399999999999999</v>
@@ -30192,7 +30189,7 @@
       </c>
     </row>
     <row r="33" spans="2:17">
-      <c r="B33" s="282"/>
+      <c r="B33" s="283"/>
       <c r="C33" s="98"/>
       <c r="D33" s="1">
         <v>0.185</v>
@@ -30238,7 +30235,7 @@
       </c>
     </row>
     <row r="34" spans="2:17">
-      <c r="B34" s="282"/>
+      <c r="B34" s="283"/>
       <c r="C34" s="99"/>
       <c r="D34" s="1">
         <v>0.32700000000000001</v>
@@ -30284,7 +30281,7 @@
       </c>
     </row>
     <row r="35" spans="2:17">
-      <c r="B35" s="282" t="s">
+      <c r="B35" s="283" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="100"/>
@@ -30332,7 +30329,7 @@
       </c>
     </row>
     <row r="36" spans="2:17">
-      <c r="B36" s="282"/>
+      <c r="B36" s="283"/>
       <c r="C36" s="101"/>
       <c r="D36" s="145">
         <v>0.20899999999999999</v>
@@ -30378,7 +30375,7 @@
       </c>
     </row>
     <row r="37" spans="2:17">
-      <c r="B37" s="282"/>
+      <c r="B37" s="283"/>
       <c r="C37" s="102"/>
       <c r="D37" s="1">
         <v>0.47699999999999998</v>
@@ -30424,7 +30421,7 @@
       </c>
     </row>
     <row r="38" spans="2:17">
-      <c r="B38" s="282"/>
+      <c r="B38" s="283"/>
       <c r="C38" s="101"/>
       <c r="D38" s="145">
         <v>0.20899999999999999</v>
@@ -30470,7 +30467,7 @@
       </c>
     </row>
     <row r="39" spans="2:17">
-      <c r="B39" s="282"/>
+      <c r="B39" s="283"/>
       <c r="C39" s="103"/>
       <c r="D39" s="1">
         <v>0.64200000000000002</v>
@@ -30516,7 +30513,7 @@
       </c>
     </row>
     <row r="40" spans="2:17">
-      <c r="B40" s="282"/>
+      <c r="B40" s="283"/>
       <c r="C40" s="104"/>
       <c r="D40" s="1">
         <v>0.6</v>
@@ -30562,7 +30559,7 @@
       </c>
     </row>
     <row r="41" spans="2:17">
-      <c r="B41" s="282"/>
+      <c r="B41" s="283"/>
       <c r="C41" s="105"/>
       <c r="D41" s="1">
         <v>0.57199999999999995</v>
@@ -30608,7 +30605,7 @@
       </c>
     </row>
     <row r="42" spans="2:17">
-      <c r="B42" s="282"/>
+      <c r="B42" s="283"/>
       <c r="C42" s="106"/>
       <c r="D42" s="1">
         <v>0.20200000000000001</v>
@@ -30654,7 +30651,7 @@
       </c>
     </row>
     <row r="43" spans="2:17">
-      <c r="B43" s="282"/>
+      <c r="B43" s="283"/>
       <c r="C43" s="107"/>
       <c r="D43" s="1">
         <v>0.152</v>
@@ -30700,7 +30697,7 @@
       </c>
     </row>
     <row r="44" spans="2:17">
-      <c r="B44" s="282"/>
+      <c r="B44" s="283"/>
       <c r="C44" s="100"/>
       <c r="D44" s="1">
         <v>0.152</v>
@@ -30746,7 +30743,7 @@
       </c>
     </row>
     <row r="45" spans="2:17">
-      <c r="B45" s="282"/>
+      <c r="B45" s="283"/>
       <c r="C45" s="108"/>
       <c r="D45" s="1">
         <v>0.19600000000000001</v>
@@ -30792,7 +30789,7 @@
       </c>
     </row>
     <row r="46" spans="2:17">
-      <c r="B46" s="282"/>
+      <c r="B46" s="283"/>
       <c r="C46" s="101"/>
       <c r="D46" s="145">
         <v>0.20899999999999999</v>
@@ -30838,7 +30835,7 @@
       </c>
     </row>
     <row r="47" spans="2:17">
-      <c r="B47" s="282" t="s">
+      <c r="B47" s="283" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="87"/>
@@ -30886,7 +30883,7 @@
       </c>
     </row>
     <row r="48" spans="2:17">
-      <c r="B48" s="282"/>
+      <c r="B48" s="283"/>
       <c r="C48" s="109"/>
       <c r="D48" s="1">
         <v>0.183</v>
@@ -30932,7 +30929,7 @@
       </c>
     </row>
     <row r="49" spans="2:17">
-      <c r="B49" s="282"/>
+      <c r="B49" s="283"/>
       <c r="C49" s="110"/>
       <c r="D49" s="1">
         <v>0.60899999999999999</v>
@@ -30978,7 +30975,7 @@
       </c>
     </row>
     <row r="50" spans="2:17">
-      <c r="B50" s="282"/>
+      <c r="B50" s="283"/>
       <c r="C50" s="110"/>
       <c r="D50" s="1">
         <v>0.60899999999999999</v>
@@ -31024,7 +31021,7 @@
       </c>
     </row>
     <row r="51" spans="2:17">
-      <c r="B51" s="282"/>
+      <c r="B51" s="283"/>
       <c r="C51" s="111"/>
       <c r="D51" s="1">
         <v>0.16600000000000001</v>
@@ -31070,7 +31067,7 @@
       </c>
     </row>
     <row r="52" spans="2:17">
-      <c r="B52" s="282"/>
+      <c r="B52" s="283"/>
       <c r="C52" s="112"/>
       <c r="D52" s="1">
         <v>0.22900000000000001</v>
@@ -31116,7 +31113,7 @@
       </c>
     </row>
     <row r="53" spans="2:17">
-      <c r="B53" s="282"/>
+      <c r="B53" s="283"/>
       <c r="C53" s="113"/>
       <c r="D53" s="1">
         <v>0.25700000000000001</v>
@@ -31162,7 +31159,7 @@
       </c>
     </row>
     <row r="54" spans="2:17">
-      <c r="B54" s="282"/>
+      <c r="B54" s="283"/>
       <c r="C54" s="114"/>
       <c r="D54" s="145">
         <v>0.35899999999999999</v>
@@ -31209,7 +31206,7 @@
       </c>
     </row>
     <row r="55" spans="2:17">
-      <c r="B55" s="282"/>
+      <c r="B55" s="283"/>
       <c r="C55" s="112"/>
       <c r="D55" s="1">
         <v>0.22800000000000001</v>
@@ -31594,16 +31591,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B15:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B46"/>
+    <mergeCell ref="B47:B55"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="B5:B14"/>
-    <mergeCell ref="B15:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B46"/>
-    <mergeCell ref="B47:B55"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
